--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -1519,17 +1519,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -1594,17 +1594,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B10" s="14" t="str">
-        <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C10" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F10" s="14" t="str">
-        <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G10" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -1669,17 +1669,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B16" s="14" t="str">
-        <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C16" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F16" s="14" t="str">
-        <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G16" s="14" t="str">
         <f>'data'!$B$4</f>
@@ -1942,17 +1942,17 @@
         <f>'data'!$B$7</f>
       </c>
       <c r="B41" s="14" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F41" s="14" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G41" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -2017,17 +2017,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B47" s="14" t="str">
-        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F47" s="14" t="str">
-        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G47" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -2092,17 +2092,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B53" s="14" t="str">
-        <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C53" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F53" s="14" t="str">
-        <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G53" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -2365,17 +2365,17 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="B78" s="14" t="str">
-        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C78" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F78" s="14" t="str">
-        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G78" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -2440,17 +2440,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B84" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C84" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D84" s="18"/>
       <c r="E84" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F84" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G84" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -2515,17 +2515,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G90" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -2904,17 +2904,17 @@
         <v>58</v>
       </c>
       <c r="B10" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C10" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F10" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G10" s="14" t="s">
         <v>58</v>
@@ -3032,17 +3032,17 @@
         <v>58</v>
       </c>
       <c r="B24" s="14" t="str">
-        <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C24" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F24" s="14" t="str">
-        <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G24" s="14" t="s">
         <v>58</v>
@@ -3160,17 +3160,17 @@
         <v>58</v>
       </c>
       <c r="B43" s="14" t="str">
-        <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F43" s="14" t="str">
-        <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G43" s="14" t="s">
         <v>58</v>
@@ -3288,17 +3288,17 @@
         <v>58</v>
       </c>
       <c r="B57" s="14" t="str">
-        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F57" s="14" t="str">
-        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G57" s="14" t="s">
         <v>58</v>
@@ -3416,17 +3416,17 @@
         <v>58</v>
       </c>
       <c r="B76" s="14" t="str">
-        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F76" s="14" t="str">
-        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G76" s="14" t="s">
         <v>58</v>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -336,7 +336,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -975,92 +975,92 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>56</v>
       </c>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -336,7 +336,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -972,7 +972,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -19,6 +19,7 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$11</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$112</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$I$19</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$9</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$86</definedName>
   </definedNames>
@@ -3465,12 +3466,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3485,13 +3491,6 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3625,10 +3624,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -531,7 +531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -3506,6 +3506,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
       </c>
@@ -3573,6 +3575,8 @@
       <c r="A14" s="24" t="str">
         <f>'data'!$A$11</f>
       </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="23" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -2829,7 +2829,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2837,7 +2837,7 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="5">
@@ -2881,7 +2881,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
@@ -2897,7 +2897,7 @@
         <v>39</v>
       </c>
       <c r="G9" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="10">
@@ -2957,7 +2957,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="B23" s="14" t="s">
         <v>39</v>
@@ -3221,7 +3221,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
       </c>
     </row>
     <row r="52">
@@ -3281,7 +3281,7 @@
         <v>39</v>
       </c>
       <c r="G56" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
       </c>
     </row>
     <row r="57">
@@ -3530,7 +3530,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3553,7 +3553,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3578,7 +3578,7 @@
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
       <c r="E14" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
       </c>
       <c r="I14" s="20"/>
     </row>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="19">
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -99,6 +99,18 @@
     <t>Pool B</t>
   </si>
   <si>
+    <t>Charlie Adams</t>
+  </si>
+  <si>
+    <t>Frank Brown</t>
+  </si>
+  <si>
+    <t>Iris Carter</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
     <t>Bob Adams</t>
   </si>
   <si>
@@ -106,18 +118,6 @@
   </si>
   <si>
     <t>Henry Carter</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Charlie Adams</t>
-  </si>
-  <si>
-    <t>Frank Brown</t>
-  </si>
-  <si>
-    <t>Iris Carter</t>
   </si>
   <si>
     <t>Shiaijo A</t>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Number of pools</t>
   </si>
@@ -72,6 +72,9 @@
     <t>Player Dojo</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -84,42 +87,69 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Dave Brown</t>
   </si>
   <si>
     <t>Team Bravo</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Grace Carter</t>
   </si>
   <si>
     <t>Team Charlie</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Pool B</t>
   </si>
   <si>
     <t>Charlie Adams</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Frank Brown</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Iris Carter</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Pool C</t>
   </si>
   <si>
     <t>Bob Adams</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Eve Brown</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Henry Carter</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -172,33 +202,6 @@
   </si>
   <si>
     <t>3.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -860,107 +863,137 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -978,92 +1011,92 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1285,7 +1318,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1296,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -1306,7 +1339,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -1316,7 +1349,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -1326,7 +1359,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -1336,7 +1369,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -1346,7 +1379,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -1419,35 +1452,35 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="D6" s="12" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D7" s="12" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="D8" s="12" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1513,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1502,22 +1535,22 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))</f>
@@ -1533,7 +1566,7 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="5">
@@ -1577,22 +1610,22 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))</f>
@@ -1608,7 +1641,7 @@
         <f>IF(UPPER(D11)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F11," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C11," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D12)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F12," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C12," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G10" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="11">
@@ -1652,22 +1685,22 @@
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B16" s="14" t="str">
         <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))),1,0))</f>
@@ -1683,7 +1716,7 @@
         <f>IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D18)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F18," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B18," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C18," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G16" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
     </row>
     <row r="17">
@@ -1727,26 +1760,26 @@
     </row>
     <row r="22">
       <c r="A22" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B23" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C7,E5:F7)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(F4&gt;B4,AND(F4=B4,E4&gt;C4)),1,0)),0)+IF(OR(COUNTA(B11:C13,E11:F13)&gt;0,D11="X",D11="x",D12="X",D12="x",D13="X",D13="x",OR(D10="X",D10="x")),IF(OR(OR(D10="X",D10="x"),AND(B10=F10,C10=E10)),0,IF(OR(F10&gt;B10,AND(F10=B10,E10&gt;C10)),1,0)),0)</f>
@@ -1766,7 +1799,7 @@
     </row>
     <row r="24">
       <c r="A24" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B24" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C7,E5:F7)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(B4&gt;F4,AND(B4=F4,C4&gt;E4)),1,0)),0)+IF(OR(COUNTA(B17:C19,E17:F19)&gt;0,D17="X",D17="x",D18="X",D18="x",D19="X",D19="x",OR(D16="X",D16="x")),IF(OR(OR(D16="X",D16="x"),AND(B16=F16,C16=E16)),0,IF(OR(F16&gt;B16,AND(F16=B16,E16&gt;C16)),1,0)),0)</f>
@@ -1786,7 +1819,7 @@
     </row>
     <row r="25">
       <c r="A25" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B25" s="14" t="str">
         <f>IF(OR(COUNTA(B11:C13,E11:F13)&gt;0,D11="X",D11="x",D12="X",D12="x",D13="X",D13="x",OR(D10="X",D10="x")),IF(OR(OR(D10="X",D10="x"),AND(B10=F10,C10=E10)),0,IF(OR(B10&gt;F10,AND(B10=F10,C10&gt;E10)),1,0)),0)+IF(OR(COUNTA(B17:C19,E17:F19)&gt;0,D17="X",D17="x",D18="X",D18="x",D19="X",D19="x",OR(D16="X",D16="x")),IF(OR(OR(D16="X",D16="x"),AND(B16=F16,C16=E16)),0,IF(OR(B16&gt;F16,AND(B16=F16,C16&gt;E16)),1,0)),0)</f>
@@ -1807,24 +1840,24 @@
     <row r="27">
       <c r="A27" s="13"/>
       <c r="B27" s="13" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B28" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C7,E5:F7)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X"),F4,0)+IF(OR(COUNTA(B11:C13,E11:F13)&gt;0,OR(D10="X",D10="x"),UPPER(D11)="X",UPPER(D12)="X",UPPER(D13)="X"),F10,0)</f>
@@ -1844,7 +1877,7 @@
     </row>
     <row r="29">
       <c r="A29" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B29" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C7,E5:F7)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X"),B4,0)+IF(OR(COUNTA(B17:C19,E17:F19)&gt;0,OR(D16="X",D16="x"),UPPER(D17)="X",UPPER(D18)="X",UPPER(D19)="X"),F16,0)</f>
@@ -1864,7 +1897,7 @@
     </row>
     <row r="30">
       <c r="A30" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B30" s="14" t="str">
         <f>IF(OR(COUNTA(B11:C13,E11:F13)&gt;0,OR(D10="X",D10="x"),UPPER(D11)="X",UPPER(D12)="X",UPPER(D13)="X"),B10,0)+IF(OR(COUNTA(B17:C19,E17:F19)&gt;0,OR(D16="X",D16="x"),UPPER(D17)="X",UPPER(D18)="X",UPPER(D19)="X"),B16,0)</f>
@@ -1885,12 +1918,12 @@
     <row r="33">
       <c r="F33" s="13"/>
       <c r="G33" s="13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34">
       <c r="F34" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G34" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(1, $G$23:$G$30, 0)), "-")</f>
@@ -1898,7 +1931,7 @@
     </row>
     <row r="35">
       <c r="F35" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G35" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(2, $G$23:$G$30, 0)), "-")</f>
@@ -1906,7 +1939,7 @@
     </row>
     <row r="36">
       <c r="F36" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G36" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(3, $G$23:$G$30, 0)), "-")</f>
@@ -1925,22 +1958,22 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B41" s="14" t="str">
         <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))),1,0))</f>
@@ -1956,7 +1989,7 @@
         <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G41" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
     </row>
     <row r="42">
@@ -2000,22 +2033,22 @@
     </row>
     <row r="46">
       <c r="A46" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B47" s="14" t="str">
         <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))),1,0))</f>
@@ -2031,7 +2064,7 @@
         <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G47" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
     </row>
     <row r="48">
@@ -2075,22 +2108,22 @@
     </row>
     <row r="52">
       <c r="A52" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
       <c r="G52" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B53" s="14" t="str">
         <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))</f>
@@ -2106,7 +2139,7 @@
         <f>IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G53" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="54">
@@ -2150,26 +2183,26 @@
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
       <c r="G59" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B60" s="14" t="str">
         <f>IF(OR(COUNTA(B42:C44,E42:F44)&gt;0,D42="X",D42="x",D43="X",D43="x",D44="X",D44="x",OR(D41="X",D41="x")),IF(OR(OR(D41="X",D41="x"),AND(B41=F41,C41=E41)),0,IF(OR(F41&gt;B41,AND(F41=B41,E41&gt;C41)),1,0)),0)+IF(OR(COUNTA(B48:C50,E48:F50)&gt;0,D48="X",D48="x",D49="X",D49="x",D50="X",D50="x",OR(D47="X",D47="x")),IF(OR(OR(D47="X",D47="x"),AND(B47=F47,C47=E47)),0,IF(OR(F47&gt;B47,AND(F47=B47,E47&gt;C47)),1,0)),0)</f>
@@ -2189,7 +2222,7 @@
     </row>
     <row r="61">
       <c r="A61" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B61" s="14" t="str">
         <f>IF(OR(COUNTA(B42:C44,E42:F44)&gt;0,D42="X",D42="x",D43="X",D43="x",D44="X",D44="x",OR(D41="X",D41="x")),IF(OR(OR(D41="X",D41="x"),AND(B41=F41,C41=E41)),0,IF(OR(B41&gt;F41,AND(B41=F41,C41&gt;E41)),1,0)),0)+IF(OR(COUNTA(B54:C56,E54:F56)&gt;0,D54="X",D54="x",D55="X",D55="x",D56="X",D56="x",OR(D53="X",D53="x")),IF(OR(OR(D53="X",D53="x"),AND(B53=F53,C53=E53)),0,IF(OR(F53&gt;B53,AND(F53=B53,E53&gt;C53)),1,0)),0)</f>
@@ -2209,7 +2242,7 @@
     </row>
     <row r="62">
       <c r="A62" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B62" s="14" t="str">
         <f>IF(OR(COUNTA(B48:C50,E48:F50)&gt;0,D48="X",D48="x",D49="X",D49="x",D50="X",D50="x",OR(D47="X",D47="x")),IF(OR(OR(D47="X",D47="x"),AND(B47=F47,C47=E47)),0,IF(OR(B47&gt;F47,AND(B47=F47,C47&gt;E47)),1,0)),0)+IF(OR(COUNTA(B54:C56,E54:F56)&gt;0,D54="X",D54="x",D55="X",D55="x",D56="X",D56="x",OR(D53="X",D53="x")),IF(OR(OR(D53="X",D53="x"),AND(B53=F53,C53=E53)),0,IF(OR(B53&gt;F53,AND(B53=F53,C53&gt;E53)),1,0)),0)</f>
@@ -2230,24 +2263,24 @@
     <row r="64">
       <c r="A64" s="13"/>
       <c r="B64" s="13" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B65" s="14" t="str">
         <f>IF(OR(COUNTA(B42:C44,E42:F44)&gt;0,OR(D41="X",D41="x"),UPPER(D42)="X",UPPER(D43)="X",UPPER(D44)="X"),F41,0)+IF(OR(COUNTA(B48:C50,E48:F50)&gt;0,OR(D47="X",D47="x"),UPPER(D48)="X",UPPER(D49)="X",UPPER(D50)="X"),F47,0)</f>
@@ -2267,7 +2300,7 @@
     </row>
     <row r="66">
       <c r="A66" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B66" s="14" t="str">
         <f>IF(OR(COUNTA(B42:C44,E42:F44)&gt;0,OR(D41="X",D41="x"),UPPER(D42)="X",UPPER(D43)="X",UPPER(D44)="X"),B41,0)+IF(OR(COUNTA(B54:C56,E54:F56)&gt;0,OR(D53="X",D53="x"),UPPER(D54)="X",UPPER(D55)="X",UPPER(D56)="X"),F53,0)</f>
@@ -2287,7 +2320,7 @@
     </row>
     <row r="67">
       <c r="A67" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B67" s="14" t="str">
         <f>IF(OR(COUNTA(B48:C50,E48:F50)&gt;0,OR(D47="X",D47="x"),UPPER(D48)="X",UPPER(D49)="X",UPPER(D50)="X"),B47,0)+IF(OR(COUNTA(B54:C56,E54:F56)&gt;0,OR(D53="X",D53="x"),UPPER(D54)="X",UPPER(D55)="X",UPPER(D56)="X"),B53,0)</f>
@@ -2308,12 +2341,12 @@
     <row r="70">
       <c r="F70" s="13"/>
       <c r="G70" s="13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71">
       <c r="F71" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G71" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(1, $G$60:$G$67, 0)), "-")</f>
@@ -2321,7 +2354,7 @@
     </row>
     <row r="72">
       <c r="F72" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G72" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(2, $G$60:$G$67, 0)), "-")</f>
@@ -2329,7 +2362,7 @@
     </row>
     <row r="73">
       <c r="F73" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G73" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(3, $G$60:$G$67, 0)), "-")</f>
@@ -2348,22 +2381,22 @@
     </row>
     <row r="77">
       <c r="A77" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
       <c r="G77" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B78" s="14" t="str">
         <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))</f>
@@ -2379,7 +2412,7 @@
         <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G78" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="79">
@@ -2423,22 +2456,22 @@
     </row>
     <row r="83">
       <c r="A83" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
       <c r="G83" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B84" s="14" t="str">
         <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))),1,0))</f>
@@ -2454,7 +2487,7 @@
         <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G84" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="85">
@@ -2498,22 +2531,22 @@
     </row>
     <row r="89">
       <c r="A89" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
       <c r="G89" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B90" s="14" t="str">
         <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))</f>
@@ -2529,7 +2562,7 @@
         <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G90" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="91">
@@ -2573,26 +2606,26 @@
     </row>
     <row r="96">
       <c r="A96" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E96" s="13"/>
       <c r="F96" s="13"/>
       <c r="G96" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B97" s="14" t="str">
         <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(F78&gt;B78,AND(F78=B78,E78&gt;C78)),1,0)),0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(F84&gt;B84,AND(F84=B84,E84&gt;C84)),1,0)),0)</f>
@@ -2612,7 +2645,7 @@
     </row>
     <row r="98">
       <c r="A98" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B98" s="14" t="str">
         <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(B78&gt;F78,AND(B78=F78,C78&gt;E78)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(F90&gt;B90,AND(F90=B90,E90&gt;C90)),1,0)),0)</f>
@@ -2632,7 +2665,7 @@
     </row>
     <row r="99">
       <c r="A99" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B99" s="14" t="str">
         <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(B84&gt;F84,AND(B84=F84,C84&gt;E84)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(B90&gt;F90,AND(B90=F90,C90&gt;E90)),1,0)),0)</f>
@@ -2653,24 +2686,24 @@
     <row r="101">
       <c r="A101" s="13"/>
       <c r="B101" s="13" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B102" s="14" t="str">
         <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),F78,0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),F84,0)</f>
@@ -2690,7 +2723,7 @@
     </row>
     <row r="103">
       <c r="A103" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B103" s="14" t="str">
         <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),B78,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),F90,0)</f>
@@ -2710,7 +2743,7 @@
     </row>
     <row r="104">
       <c r="A104" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B104" s="14" t="str">
         <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),B84,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),B90,0)</f>
@@ -2731,12 +2764,12 @@
     <row r="107">
       <c r="F107" s="13"/>
       <c r="G107" s="13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108">
       <c r="F108" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G108" s="19" t="str">
         <f>IFERROR(INDEX($A$97:$A$104, MATCH(1, $G$97:$G$104, 0)), "-")</f>
@@ -2744,7 +2777,7 @@
     </row>
     <row r="109">
       <c r="F109" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G109" s="19" t="str">
         <f>IFERROR(INDEX($A$97:$A$104, MATCH(2, $G$97:$G$104, 0)), "-")</f>
@@ -2752,7 +2785,7 @@
     </row>
     <row r="110">
       <c r="F110" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G110" s="19" t="str">
         <f>IFERROR(INDEX($A$97:$A$104, MATCH(3, $G$97:$G$104, 0)), "-")</f>
@@ -2796,7 +2829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2807,7 +2840,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2818,13 +2851,13 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2884,17 +2917,17 @@
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
       </c>
       <c r="B9" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G9" s="14" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
@@ -2902,7 +2935,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))</f>
@@ -2918,24 +2951,24 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G10" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="F13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G13" s="19"/>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G14" s="19"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2946,13 +2979,13 @@
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -3012,17 +3045,17 @@
         <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="B23" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G23" s="14" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
@@ -3030,7 +3063,7 @@
     </row>
     <row r="24">
       <c r="A24" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="14" t="str">
         <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))</f>
@@ -3046,24 +3079,24 @@
         <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G24" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="F27" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G27" s="19"/>
     </row>
     <row r="28">
       <c r="F28" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G28" s="19"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3074,13 +3107,13 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
@@ -3140,17 +3173,17 @@
         <f>CONCATENATE("M 1 ",G13)</f>
       </c>
       <c r="B42" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G42" s="14" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
@@ -3158,7 +3191,7 @@
     </row>
     <row r="43">
       <c r="A43" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" s="14" t="str">
         <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))</f>
@@ -3174,24 +3207,24 @@
         <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G43" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
       <c r="F46" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G46" s="19"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G47" s="19"/>
     </row>
     <row r="49">
       <c r="A49" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -3202,13 +3235,13 @@
     </row>
     <row r="50">
       <c r="A50" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
@@ -3268,17 +3301,17 @@
         <f>CONCATENATE("M 2 ",G27)</f>
       </c>
       <c r="B56" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D56" s="14"/>
       <c r="E56" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G56" s="14" t="str">
         <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
@@ -3286,7 +3319,7 @@
     </row>
     <row r="57">
       <c r="A57" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57" s="14" t="str">
         <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))</f>
@@ -3302,24 +3335,24 @@
         <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G57" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
       <c r="F60" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G60" s="19"/>
     </row>
     <row r="61">
       <c r="F61" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G61" s="19"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
@@ -3330,13 +3363,13 @@
     </row>
     <row r="69">
       <c r="A69" s="17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
@@ -3396,17 +3429,17 @@
         <f>CONCATENATE("M 4 ",G60)</f>
       </c>
       <c r="B75" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G75" s="14" t="str">
         <f>CONCATENATE("M 3 ",G46)</f>
@@ -3414,7 +3447,7 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B76" s="14" t="str">
         <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))</f>
@@ -3430,18 +3463,18 @@
         <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G76" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79">
       <c r="F79" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G79" s="19"/>
     </row>
     <row r="80">
       <c r="F80" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G80" s="19"/>
     </row>
@@ -3499,12 +3532,12 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -3514,7 +3547,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
@@ -3538,7 +3571,7 @@
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -3550,7 +3583,7 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
@@ -3561,7 +3594,7 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="I12" s="21">
         <v>5</v>
@@ -3584,7 +3617,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="F15" s="22"/>
       <c r="G15" s="20"/>
@@ -3592,7 +3625,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="G16" s="21">
         <v>4</v>
@@ -3602,7 +3635,7 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
@@ -3644,72 +3677,72 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>48</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$D$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>49</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$D$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>50</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$D$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>51</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$D$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>52</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$D$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>53</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$D$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>54</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$D$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>55</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$D$10</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>56</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$D$11</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!$B$11</f>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -18,17 +18,17 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$11</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$112</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$I$19</definedName>
-    <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$9</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$86</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$75</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$G$13</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$6</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Number of pools</t>
   </si>
@@ -78,46 +78,43 @@
     <t>Pool A</t>
   </si>
   <si>
-    <t>Alice Adams</t>
-  </si>
-  <si>
     <t>Team Alpha</t>
   </si>
   <si>
-    <t>Dave Brown</t>
+    <t>Enzan Dojo</t>
+  </si>
+  <si>
+    <t>Team Charlie</t>
+  </si>
+  <si>
+    <t>Seishin Dojo</t>
+  </si>
+  <si>
+    <t>Team Echo</t>
+  </si>
+  <si>
+    <t>Kenshin Dojo</t>
+  </si>
+  <si>
+    <t>Pool B</t>
   </si>
   <si>
     <t>Team Bravo</t>
   </si>
   <si>
-    <t>Grace Carter</t>
-  </si>
-  <si>
-    <t>Team Charlie</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Charlie Adams</t>
-  </si>
-  <si>
-    <t>Frank Brown</t>
-  </si>
-  <si>
-    <t>Iris Carter</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Bob Adams</t>
-  </si>
-  <si>
-    <t>Eve Brown</t>
-  </si>
-  <si>
-    <t>Henry Carter</t>
+    <t>Mushin Dojo</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>Fudoshin Dojo</t>
+  </si>
+  <si>
+    <t>Team Foxtrot</t>
+  </si>
+  <si>
+    <t>Hakuun Dojo</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -192,15 +189,6 @@
     <t>B3</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
     <t>Round 1 - Match 1</t>
   </si>
   <si>
@@ -211,12 +199,6 @@
   </si>
   <si>
     <t>Round 2 - Match 3</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 4</t>
-  </si>
-  <si>
-    <t>Round 3 - Match 5</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -905,7 +887,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +895,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -924,43 +906,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -978,108 +927,75 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" ht="409" customHeight="true">
-      <c r="A13" s="30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" ht="409" customHeight="true">
-      <c r="A14" s="30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="409" customHeight="true">
-      <c r="A15" s="30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" ht="409" customHeight="true">
-      <c r="A16" s="30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" ht="409" customHeight="true">
-      <c r="A17" s="30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" ht="409" customHeight="true">
-      <c r="A18" s="30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <rowBreaks count="9" manualBreakCount="9">
+  <rowBreaks count="6" manualBreakCount="6">
     <brk id="2" max="16383" man="true"/>
     <brk id="4" max="16383" man="true"/>
     <brk id="6" max="16383" man="true"/>
     <brk id="8" max="16383" man="true"/>
     <brk id="10" max="16383" man="true"/>
     <brk id="12" max="16383" man="true"/>
-    <brk id="14" max="16383" man="true"/>
-    <brk id="16" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>
@@ -1125,13 +1041,13 @@
     </row>
     <row r="2" ht="16" customHeight="true">
       <c r="A2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3">
         <v>0.0020833333333333333</v>
@@ -1231,7 +1147,7 @@
     </row>
     <row r="8" ht="16" customHeight="true">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -1285,7 +1201,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1296,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -1306,7 +1222,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -1316,7 +1232,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -1326,7 +1242,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -1336,7 +1252,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -1346,7 +1262,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -1374,7 +1290,6 @@
     <col customWidth="true" max="3" min="3" width="8.83"/>
     <col customWidth="true" max="4" min="4" width="30"/>
     <col customWidth="true" max="5" min="5" width="8.83"/>
-    <col customWidth="true" max="6" min="6" width="30"/>
     <col customWidth="true" max="7" min="7" width="8.83"/>
   </cols>
   <sheetData>
@@ -1413,9 +1328,6 @@
       <c r="D5" s="11" t="str">
         <f>'data'!$A$8</f>
       </c>
-      <c r="F5" s="11" t="str">
-        <f>'data'!$A$11</f>
-      </c>
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
@@ -1424,9 +1336,6 @@
       <c r="D6" s="12" t="str">
         <f>"1. " &amp; data!$B$6</f>
       </c>
-      <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$9</f>
-      </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
@@ -1435,9 +1344,6 @@
       <c r="D7" s="12" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
-      <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$10</f>
-      </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
@@ -1445,9 +1351,6 @@
       </c>
       <c r="D8" s="12" t="str">
         <f>"3. " &amp; data!$B$8</f>
-      </c>
-      <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$11</f>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1383,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1502,17 +1405,17 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -1577,17 +1480,17 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -1652,17 +1555,17 @@
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1727,21 +1630,21 @@
     </row>
     <row r="22">
       <c r="A22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>37</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -1807,19 +1710,19 @@
     <row r="27">
       <c r="A27" s="13"/>
       <c r="B27" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="E27" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="F27" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -1885,12 +1788,12 @@
     <row r="33">
       <c r="F33" s="13"/>
       <c r="G33" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="F34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G34" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(1, $G$23:$G$30, 0)), "-")</f>
@@ -1898,7 +1801,7 @@
     </row>
     <row r="35">
       <c r="F35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(2, $G$23:$G$30, 0)), "-")</f>
@@ -1906,7 +1809,7 @@
     </row>
     <row r="36">
       <c r="F36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G36" s="19" t="str">
         <f>IFERROR(INDEX($A$23:$A$30, MATCH(3, $G$23:$G$30, 0)), "-")</f>
@@ -1925,17 +1828,17 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -2000,17 +1903,17 @@
     </row>
     <row r="46">
       <c r="A46" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -2075,17 +1978,17 @@
     </row>
     <row r="52">
       <c r="A52" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
       <c r="G52" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2150,21 +2053,21 @@
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="C59" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>37</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
       <c r="G59" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
@@ -2230,19 +2133,19 @@
     <row r="64">
       <c r="A64" s="13"/>
       <c r="B64" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="D64" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="E64" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="F64" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="65">
@@ -2308,12 +2211,12 @@
     <row r="70">
       <c r="F70" s="13"/>
       <c r="G70" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="F71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G71" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(1, $G$60:$G$67, 0)), "-")</f>
@@ -2321,7 +2224,7 @@
     </row>
     <row r="72">
       <c r="F72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G72" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(2, $G$60:$G$67, 0)), "-")</f>
@@ -2329,448 +2232,23 @@
     </row>
     <row r="73">
       <c r="F73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G73" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$67, MATCH(3, $G$60:$G$67, 0)), "-")</f>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="13" t="str">
-        <f>'data'!$A$11</f>
-      </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-      <c r="B78" s="14" t="str">
-        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C78" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D78" s="18"/>
-      <c r="E78" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F78" s="14" t="str">
-        <f>IF(UPPER(D79)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G78" s="14" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14">
-        <v>1</v>
-      </c>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14">
-        <v>2</v>
-      </c>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14">
-        <v>3</v>
-      </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-      <c r="B84" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C84" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D84" s="18"/>
-      <c r="E84" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F84" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G84" s="14" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="14">
-        <v>1</v>
-      </c>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14">
-        <v>2</v>
-      </c>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="14">
-        <v>3</v>
-      </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="14"/>
-      <c r="D89" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="14" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-      <c r="B90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D90" s="18"/>
-      <c r="E90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G90" s="14" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="14">
-        <v>1</v>
-      </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="14">
-        <v>2</v>
-      </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14">
-        <v>3</v>
-      </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(F78&gt;B78,AND(F78=B78,E78&gt;C78)),1,0)),0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(F84&gt;B84,AND(F84=B84,E84&gt;C84)),1,0)),0)</f>
-      </c>
-      <c r="C97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(F78&lt;B78,AND(F78=B78,E78&lt;C78)),1,0)),0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(F84&lt;B84,AND(F84=B84,E84&lt;C84)),1,0)),0)</f>
-      </c>
-      <c r="D97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),1,0),0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),1,0),0)</f>
-      </c>
-      <c r="G97" s="18" t="str">
-        <f>RANK(U97,$U$97:$U$99)+COUNTIF($U$96:U96,U97)</f>
-      </c>
-      <c r="U97" t="str">
-        <f>(B97*1000000000)-(C97*10000000)+(D97*100000)+(B102*1000)-(C102*100)+(D102*10)+(E102*1)-(F102*0.01)</f>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="14" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-      <c r="B98" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(B78&gt;F78,AND(B78=F78,C78&gt;E78)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(F90&gt;B90,AND(F90=B90,E90&gt;C90)),1,0)),0)</f>
-      </c>
-      <c r="C98" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),0,IF(OR(B78&lt;F78,AND(B78=F78,C78&lt;E78)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(F90&lt;B90,AND(F90=B90,E90&lt;C90)),1,0)),0)</f>
-      </c>
-      <c r="D98" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,D79="X",D79="x",D80="X",D80="x",D81="X",D81="x",OR(D78="X",D78="x")),IF(OR(OR(D78="X",D78="x"),AND(B78=F78,C78=E78)),1,0),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),1,0),0)</f>
-      </c>
-      <c r="G98" s="18" t="str">
-        <f>RANK(U98,$U$97:$U$99)+COUNTIF($U$96:U97,U98)</f>
-      </c>
-      <c r="U98" t="str">
-        <f>(B98*1000000000)-(C98*10000000)+(D98*100000)+(B103*1000)-(C103*100)+(D103*10)+(E103*1)-(F103*0.01)</f>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-      <c r="B99" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(B84&gt;F84,AND(B84=F84,C84&gt;E84)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(B90&gt;F90,AND(B90=F90,C90&gt;E90)),1,0)),0)</f>
-      </c>
-      <c r="C99" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),0,IF(OR(B84&lt;F84,AND(B84=F84,C84&lt;E84)),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),0,IF(OR(B90&lt;F90,AND(B90=F90,C90&lt;E90)),1,0)),0)</f>
-      </c>
-      <c r="D99" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,D85="X",D85="x",D86="X",D86="x",D87="X",D87="x",OR(D84="X",D84="x")),IF(OR(OR(D84="X",D84="x"),AND(B84=F84,C84=E84)),1,0),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",OR(D90="X",D90="x")),IF(OR(OR(D90="X",D90="x"),AND(B90=F90,C90=E90)),1,0),0)</f>
-      </c>
-      <c r="G99" s="18" t="str">
-        <f>RANK(U99,$U$97:$U$99)+COUNTIF($U$96:U98,U99)</f>
-      </c>
-      <c r="U99" t="str">
-        <f>(B99*1000000000)-(C99*10000000)+(D99*100000)+(B104*1000)-(C104*100)+(D104*10)+(E104*1)-(F104*0.01)</f>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="13"/>
-      <c r="B101" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="14" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),F78,0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),F84,0)</f>
-      </c>
-      <c r="C102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),B78,0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),B84,0)</f>
-      </c>
-      <c r="D102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),(IF(OR(D79="X",D79="x",AND(COUNTA(B79,C79,E79,F79)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))))),1,0)+IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),(IF(OR(D85="X",D85="x",AND(COUNTA(B85,C85,E85,F85)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))))),1,0)+IF(OR(D86="X",D86="x",AND(COUNTA(B86,C86,E86,F86)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))))),1,0)+IF(OR(D87="X",D87="x",AND(COUNTA(B87,C87,E87,F87)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E102" s="14" t="str">
-        <f>E78+E84</f>
-      </c>
-      <c r="F102" s="14" t="str">
-        <f>C78+C84</f>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="14" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-      <c r="B103" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),B78,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),F90,0)</f>
-      </c>
-      <c r="C103" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),F78,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),B90,0)</f>
-      </c>
-      <c r="D103" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C81,E79:F81)&gt;0,OR(D78="X",D78="x"),UPPER(D79)="X",UPPER(D80)="X",UPPER(D81)="X"),(IF(OR(D79="X",D79="x",AND(COUNTA(B79,C79,E79,F79)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79," ",""),"0",""),"-",""))))),1,0)+IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),(IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)+IF(OR(D93="X",D93="x",AND(COUNTA(B93,C93,E93,F93)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E103" s="14" t="str">
-        <f>C78+E90</f>
-      </c>
-      <c r="F103" s="14" t="str">
-        <f>E78+C90</f>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="14" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-      <c r="B104" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),B84,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),B90,0)</f>
-      </c>
-      <c r="C104" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),F84,0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),F90,0)</f>
-      </c>
-      <c r="D104" s="14" t="str">
-        <f>IF(OR(COUNTA(B85:C87,E85:F87)&gt;0,OR(D84="X",D84="x"),UPPER(D85)="X",UPPER(D86)="X",UPPER(D87)="X"),(IF(OR(D85="X",D85="x",AND(COUNTA(B85,C85,E85,F85)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))))),1,0)+IF(OR(D86="X",D86="x",AND(COUNTA(B86,C86,E86,F86)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))))),1,0)+IF(OR(D87="X",D87="x",AND(COUNTA(B87,C87,E87,F87)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B91:C93,E91:F93)&gt;0,OR(D90="X",D90="x"),UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X"),(IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)+IF(OR(D93="X",D93="x",AND(COUNTA(B93,C93,E93,F93)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E104" s="14" t="str">
-        <f>C84+C90</f>
-      </c>
-      <c r="F104" s="14" t="str">
-        <f>E84+E90</f>
-      </c>
-    </row>
-    <row r="107">
-      <c r="F107" s="13"/>
-      <c r="G107" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="F108" t="s">
-        <v>45</v>
-      </c>
-      <c r="G108" s="19" t="str">
-        <f>IFERROR(INDEX($A$97:$A$104, MATCH(1, $G$97:$G$104, 0)), "-")</f>
-      </c>
-    </row>
-    <row r="109">
-      <c r="F109" t="s">
-        <v>46</v>
-      </c>
-      <c r="G109" s="19" t="str">
-        <f>IFERROR(INDEX($A$97:$A$104, MATCH(2, $G$97:$G$104, 0)), "-")</f>
-      </c>
-    </row>
-    <row r="110">
-      <c r="F110" t="s">
-        <v>47</v>
-      </c>
-      <c r="G110" s="19" t="str">
-        <f>IFERROR(INDEX($A$97:$A$104, MATCH(3, $G$97:$G$104, 0)), "-")</f>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A76:G76"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks count="2" manualBreakCount="2">
+  <rowBreaks count="1" manualBreakCount="1">
     <brk id="38" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>
@@ -2796,7 +2274,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2807,7 +2285,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2818,18 +2296,18 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="G3" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2837,7 +2315,7 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
       </c>
     </row>
     <row r="5">
@@ -2881,28 +2359,28 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
       </c>
       <c r="B9" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))</f>
@@ -2918,24 +2396,24 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G10" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" s="19"/>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="19"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2946,18 +2424,18 @@
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="G17" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -2965,7 +2443,7 @@
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="19">
@@ -3009,28 +2487,28 @@
     </row>
     <row r="23">
       <c r="A23" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
       </c>
       <c r="B23" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B24" s="14" t="str">
         <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))</f>
@@ -3046,24 +2524,24 @@
         <f>IF(UPPER(D19)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F19," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C19," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D20)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G24" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="F27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G27" s="19"/>
     </row>
     <row r="28">
       <c r="F28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="19"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3074,18 +2552,18 @@
     </row>
     <row r="36">
       <c r="A36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="G36" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G13)</f>
+        <f>CONCATENATE("M 2 ",G27)</f>
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -3093,7 +2571,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
       <c r="G37" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
+        <f>CONCATENATE("M 1 ",G13)</f>
       </c>
     </row>
     <row r="38">
@@ -3137,28 +2615,28 @@
     </row>
     <row r="42">
       <c r="A42" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G13)</f>
+        <f>CONCATENATE("M 2 ",G27)</f>
       </c>
       <c r="B42" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G42" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
+        <f>CONCATENATE("M 1 ",G13)</f>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B43" s="14" t="str">
         <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))</f>
@@ -3174,292 +2652,33 @@
         <f>IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G43" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46">
       <c r="F46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G46" s="19"/>
     </row>
     <row r="47">
       <c r="F47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="19"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G27)</f>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14">
-        <v>1</v>
-      </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14">
-        <v>2</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14">
-        <v>3</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G27)</f>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="14" t="str">
-        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F57" s="14" t="str">
-        <f>IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="F60" t="s">
-        <v>45</v>
-      </c>
-      <c r="G60" s="19"/>
-    </row>
-    <row r="61">
-      <c r="F61" t="s">
-        <v>46</v>
-      </c>
-      <c r="G61" s="19"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G60)</f>
-      </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G46)</f>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14">
-        <v>1</v>
-      </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14">
-        <v>2</v>
-      </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14">
-        <v>3</v>
-      </c>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G60)</f>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G46)</f>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B76" s="14" t="str">
-        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F76" s="14" t="str">
-        <f>IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="F79" t="s">
-        <v>45</v>
-      </c>
-      <c r="G79" s="19"/>
-    </row>
-    <row r="80">
-      <c r="F80" t="s">
-        <v>46</v>
-      </c>
-      <c r="G80" s="19"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A68:G68"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks count="2" manualBreakCount="2">
+  <rowBreaks count="1" manualBreakCount="1">
     <brk id="34" max="16383" man="true"/>
-    <brk id="67" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>
@@ -3489,8 +2708,6 @@
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3501,21 +2718,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G34)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -3533,8 +2757,6 @@
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G71)</f>
       </c>
       <c r="G9" s="20"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="20"/>
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
@@ -3542,93 +2764,33 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
-      <c r="I10" s="20"/>
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
-      <c r="I11" s="20"/>
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="I12" s="21">
-        <v>5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="22"/>
-      <c r="I13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="str">
-        <f>'data'!$A$11</f>
-      </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G108)</f>
-      </c>
-      <c r="I14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$9</f>
-      </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="20"/>
-      <c r="I15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$10</f>
-      </c>
-      <c r="G16" s="21">
-        <v>4</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$11</f>
-      </c>
-      <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G35)</f>
-      </c>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="21">
-        <v>2</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G72)</f>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
@@ -3645,7 +2807,7 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!$B$3</f>
@@ -3653,7 +2815,7 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!$B$4</f>
@@ -3661,7 +2823,7 @@
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!$B$5</f>
@@ -3669,7 +2831,7 @@
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!$B$6</f>
@@ -3677,7 +2839,7 @@
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!$B$7</f>
@@ -3685,44 +2847,19 @@
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!$B$8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="29" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="29" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="29" t="str">
-        <f>'data'!$B$11</f>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="3" manualBreakCount="3">
+  <rowBreaks count="2" manualBreakCount="2">
     <brk id="3" max="16383" man="true"/>
     <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -21,6 +21,7 @@
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$H$112</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$I$19</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$9</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tags'!$A$1:$A$18</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$86</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -550,13 +551,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1006,7 +1007,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -554,7 +554,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -3673,8 +3673,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-teams-of-3-round-robin.xlsx
+++ b/pools-example-teams-of-3-round-robin.xlsx
@@ -557,7 +557,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
